--- a/artfynd/A 52575-2022 artfynd.xlsx
+++ b/artfynd/A 52575-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113712681</v>
+        <v>113714887</v>
       </c>
       <c r="B2" t="n">
         <v>90149</v>

--- a/artfynd/A 52575-2022 artfynd.xlsx
+++ b/artfynd/A 52575-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113714887</v>
       </c>
       <c r="B2" t="n">
-        <v>90149</v>
+        <v>90153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52575-2022 artfynd.xlsx
+++ b/artfynd/A 52575-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714887</v>
+        <v>113712681</v>
       </c>
       <c r="B2" t="n">
         <v>90153</v>

--- a/artfynd/A 52575-2022 artfynd.xlsx
+++ b/artfynd/A 52575-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113712681</v>
+        <v>113714887</v>
       </c>
       <c r="B2" t="n">
         <v>90153</v>

--- a/artfynd/A 52575-2022 artfynd.xlsx
+++ b/artfynd/A 52575-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52575-2022 artfynd.xlsx
+++ b/artfynd/A 52575-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,103 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133742410</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58822</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>637901</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7034000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52575-2022 artfynd.xlsx
+++ b/artfynd/A 52575-2022 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>133742410</v>
       </c>
       <c r="B3" t="n">
-        <v>58822</v>
+        <v>58829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52575-2022 artfynd.xlsx
+++ b/artfynd/A 52575-2022 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>133742410</v>
       </c>
       <c r="B3" t="n">
-        <v>58829</v>
+        <v>58839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 52575-2022 artfynd.xlsx
+++ b/artfynd/A 52575-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712680</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133739170</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661896</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661897</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661899</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661900</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661901</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661904</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661905</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661887</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133742410</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,8 +1905,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661908</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>